--- a/Result/profitability/3040.xlsx
+++ b/Result/profitability/3040.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.83</v>
       </c>
       <c r="M2" t="n">
-        <v>0.19625</v>
+        <v>0.16375</v>
       </c>
       <c r="N2" t="n">
-        <v>54.73500000000001</v>
+        <v>55.21</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.3</v>
       </c>
       <c r="M3" t="n">
-        <v>0.21875</v>
+        <v>0.17</v>
       </c>
       <c r="N3" t="n">
-        <v>50.83375</v>
+        <v>51.56625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.34</v>
       </c>
       <c r="M4" t="n">
-        <v>0.23</v>
+        <v>0.15125</v>
       </c>
       <c r="N4" t="n">
-        <v>47.9925</v>
+        <v>49.27500000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.3</v>
       </c>
       <c r="M5" t="n">
-        <v>0.13125</v>
+        <v>0.12625</v>
       </c>
       <c r="N5" t="n">
-        <v>44.76625</v>
+        <v>44.54375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.08</v>
       </c>
       <c r="M6" t="n">
-        <v>0.15375</v>
+        <v>0.14625</v>
       </c>
       <c r="N6" t="n">
-        <v>41.2825</v>
+        <v>42.18625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.09</v>
       </c>
       <c r="M7" t="n">
-        <v>0.175</v>
+        <v>0.155</v>
       </c>
       <c r="N7" t="n">
-        <v>40.12875</v>
+        <v>40.76499999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.21</v>
       </c>
       <c r="M8" t="n">
-        <v>0.19875</v>
+        <v>0.17625</v>
       </c>
       <c r="N8" t="n">
-        <v>37.61625</v>
+        <v>38.24625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>31</v>
+      </c>
+      <c r="D75" t="n">
+        <v>11</v>
+      </c>
+      <c r="E75" t="n">
+        <v>19</v>
+      </c>
+      <c r="F75" t="n">
+        <v>63.16</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.51%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="N75" t="n">
+        <v>58.7225</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.039999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.08671713695801797</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.04000000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.780000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.02740991684631966</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
